--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_individual_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_individual_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.008439271833561955</v>
       </c>
       <c r="C2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>18890455</v>
+        <v>4500497</v>
       </c>
       <c r="L2" t="n">
-        <v>11325457</v>
+        <v>2505308</v>
       </c>
       <c r="M2" t="n">
-        <v>2750670</v>
+        <v>586433</v>
       </c>
       <c r="N2" t="n">
-        <v>132905</v>
+        <v>21953</v>
       </c>
       <c r="O2" t="n">
-        <v>1605027</v>
+        <v>337178</v>
       </c>
       <c r="P2" t="n">
-        <v>628144</v>
+        <v>140360</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998933076858521</v>
+        <v>0.9998970627784729</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9290746450424194</v>
+        <v>0.8759963512420654</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8505563735961914</v>
+        <v>0.7610160112380981</v>
       </c>
       <c r="T2" t="n">
-        <v>0.820864200592041</v>
+        <v>0.6919938921928406</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2826761603355408</v>
+        <v>0.1826585531234741</v>
       </c>
       <c r="V2" t="n">
-        <v>0.844021201133728</v>
+        <v>0.7466975450515747</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9062283039093018</v>
+        <v>0.8397700190544128</v>
       </c>
       <c r="X2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="AG2" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AH2" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AI2" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566228985786438</v>
+        <v>0.956451416015625</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112591743469238</v>
+        <v>0.9113048315048218</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.858102023601532</v>
+        <v>0.8578755855560303</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624639630317688</v>
+        <v>0.6619618535041809</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020282030105591</v>
+        <v>0.9019733667373657</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002023734838753813</v>
       </c>
       <c r="C3" t="n">
-        <v>800</v>
+        <v>204</v>
       </c>
       <c r="D3" t="n">
-        <v>18890455</v>
+        <v>4500497</v>
       </c>
       <c r="E3" t="n">
-        <v>1219323</v>
+        <v>515379</v>
       </c>
       <c r="F3" t="n">
-        <v>11897</v>
+        <v>6151</v>
       </c>
       <c r="G3" t="n">
-        <v>1883</v>
+        <v>747</v>
       </c>
       <c r="H3" t="n">
-        <v>555</v>
+        <v>239</v>
       </c>
       <c r="I3" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>40063794</v>
+        <v>10015972</v>
       </c>
       <c r="K3" t="n">
-        <v>43751340</v>
+        <v>10669293</v>
       </c>
       <c r="L3" t="n">
-        <v>50280757</v>
+        <v>12273964</v>
       </c>
       <c r="M3" t="n">
-        <v>60990249</v>
+        <v>15135988</v>
       </c>
       <c r="N3" t="n">
-        <v>64624749</v>
+        <v>16142176</v>
       </c>
       <c r="O3" t="n">
-        <v>62985470</v>
+        <v>15705841</v>
       </c>
       <c r="P3" t="n">
-        <v>64480211</v>
+        <v>16109473</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9386577010154724</v>
+        <v>0.8959370851516724</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8680008053779602</v>
+        <v>0.7664101123809814</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7378650307655334</v>
+        <v>0.6288211941719055</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3729211688041687</v>
+        <v>0.2461346983909607</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7882021069526672</v>
+        <v>0.6619406342506409</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8124036192893982</v>
+        <v>0.7259524464607239</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="Z3" t="n">
-        <v>791602</v>
+        <v>198076</v>
       </c>
       <c r="AA3" t="n">
-        <v>34131</v>
+        <v>8559</v>
       </c>
       <c r="AB3" t="n">
-        <v>27146</v>
+        <v>6810</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40066488</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>44319573</v>
+        <v>11087378</v>
       </c>
       <c r="AG3" t="n">
-        <v>51114353</v>
+        <v>12771195</v>
       </c>
       <c r="AH3" t="n">
-        <v>61061800</v>
+        <v>15264532</v>
       </c>
       <c r="AI3" t="n">
-        <v>64841808</v>
+        <v>16210280</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63082667</v>
+        <v>15770309</v>
       </c>
       <c r="AK3" t="n">
-        <v>64492192</v>
+        <v>16123000</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576059579849243</v>
+        <v>0.9574934840202332</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100238084793091</v>
+        <v>0.909995973110199</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576881885528564</v>
+        <v>0.857442319393158</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66196209192276</v>
+        <v>0.6615017056465149</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016556143760681</v>
+        <v>0.9016192555427551</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03193050064849949</v>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>1349811</v>
+        <v>601553</v>
       </c>
       <c r="E4" t="n">
-        <v>11325457</v>
+        <v>2505308</v>
       </c>
       <c r="F4" t="n">
-        <v>346475</v>
+        <v>147023</v>
       </c>
       <c r="G4" t="n">
-        <v>12610</v>
+        <v>6594</v>
       </c>
       <c r="H4" t="n">
-        <v>12486</v>
+        <v>7796</v>
       </c>
       <c r="I4" t="n">
-        <v>874</v>
+        <v>593</v>
       </c>
       <c r="J4" t="n">
-        <v>2694</v>
+        <v>650</v>
       </c>
       <c r="K4" t="n">
-        <v>1442093</v>
+        <v>637078</v>
       </c>
       <c r="L4" t="n">
-        <v>1989894</v>
+        <v>786749</v>
       </c>
       <c r="M4" t="n">
-        <v>600274</v>
+        <v>261021</v>
       </c>
       <c r="N4" t="n">
-        <v>337262</v>
+        <v>98233</v>
       </c>
       <c r="O4" t="n">
-        <v>296616</v>
+        <v>114381</v>
       </c>
       <c r="P4" t="n">
-        <v>64997</v>
+        <v>26781</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999946653842926</v>
+        <v>0.9999485611915588</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9338415861129761</v>
+        <v>0.8858544826507568</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8591901063919067</v>
+        <v>0.7637035250663757</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7771548628807068</v>
+        <v>0.658896803855896</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3215874135494232</v>
+        <v>0.2096982896327972</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8151571750640869</v>
+        <v>0.7017691731452942</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8567548990249634</v>
+        <v>0.7787243127822876</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>815845</v>
+        <v>204447</v>
       </c>
       <c r="Z4" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AA4" t="n">
-        <v>331353</v>
+        <v>83051</v>
       </c>
       <c r="AB4" t="n">
-        <v>21937</v>
+        <v>5499</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>873860</v>
+        <v>218993</v>
       </c>
       <c r="AG4" t="n">
-        <v>1156298</v>
+        <v>289518</v>
       </c>
       <c r="AH4" t="n">
-        <v>528723</v>
+        <v>132477</v>
       </c>
       <c r="AI4" t="n">
-        <v>120203</v>
+        <v>30129</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199419</v>
+        <v>49913</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571141600608826</v>
+        <v>0.9569721221923828</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910641074180603</v>
+        <v>0.9106499552726746</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578950166702271</v>
+        <v>0.857658863067627</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622129082679749</v>
+        <v>0.6617317199707031</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018418788909912</v>
+        <v>0.9017962217330933</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>739</v>
+        <v>198</v>
       </c>
       <c r="D5" t="n">
-        <v>56754</v>
+        <v>21880</v>
       </c>
       <c r="E5" t="n">
-        <v>669623</v>
+        <v>238765</v>
       </c>
       <c r="F5" t="n">
-        <v>2750670</v>
+        <v>586433</v>
       </c>
       <c r="G5" t="n">
-        <v>129240</v>
+        <v>31241</v>
       </c>
       <c r="H5" t="n">
-        <v>114616</v>
+        <v>50207</v>
       </c>
       <c r="I5" t="n">
-        <v>6235</v>
+        <v>3867</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1234512</v>
+        <v>522732</v>
       </c>
       <c r="L5" t="n">
-        <v>1722292</v>
+        <v>763579</v>
       </c>
       <c r="M5" t="n">
-        <v>977207</v>
+        <v>346158</v>
       </c>
       <c r="N5" t="n">
-        <v>223484</v>
+        <v>67238</v>
       </c>
       <c r="O5" t="n">
-        <v>431287</v>
+        <v>172200</v>
       </c>
       <c r="P5" t="n">
-        <v>145048</v>
+        <v>52986</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999587535858154</v>
+        <v>0.99996018409729</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9590221643447876</v>
+        <v>0.928974986076355</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9431678652763367</v>
+        <v>0.9050602316856384</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9758493900299072</v>
+        <v>0.9628172516822815</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9914152026176453</v>
+        <v>0.9898667931556702</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9888560771942139</v>
+        <v>0.9824501872062683</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9967842698097229</v>
+        <v>0.9951151609420776</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32012</v>
+        <v>8028</v>
       </c>
       <c r="Z5" t="n">
-        <v>339750</v>
+        <v>85185</v>
       </c>
       <c r="AA5" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AB5" t="n">
-        <v>39755</v>
+        <v>9960</v>
       </c>
       <c r="AC5" t="n">
-        <v>116472</v>
+        <v>29142</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>853179</v>
+        <v>213520</v>
       </c>
       <c r="AG5" t="n">
-        <v>1173987</v>
+        <v>294213</v>
       </c>
       <c r="AH5" t="n">
-        <v>530521</v>
+        <v>132948</v>
       </c>
       <c r="AI5" t="n">
-        <v>120473</v>
+        <v>30191</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200260</v>
+        <v>50113</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735596776008606</v>
+        <v>0.9735135436058044</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643242359161377</v>
+        <v>0.9642531871795654</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837833642959595</v>
+        <v>0.9837457537651062</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963153600692749</v>
+        <v>0.9963061213493347</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938810467720032</v>
+        <v>0.9938745498657227</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998375415802002</v>
+        <v>0.9983739256858826</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="D6" t="n">
-        <v>35298</v>
+        <v>13562</v>
       </c>
       <c r="E6" t="n">
-        <v>79844</v>
+        <v>18451</v>
       </c>
       <c r="F6" t="n">
-        <v>72215</v>
+        <v>25516</v>
       </c>
       <c r="G6" t="n">
-        <v>132905</v>
+        <v>21953</v>
       </c>
       <c r="H6" t="n">
-        <v>34352</v>
+        <v>8954</v>
       </c>
       <c r="I6" t="n">
-        <v>1627</v>
+        <v>716</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25780</v>
+        <v>6462</v>
       </c>
       <c r="Z6" t="n">
-        <v>21382</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>43482</v>
+        <v>10898</v>
       </c>
       <c r="AB6" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AC6" t="n">
-        <v>27905</v>
+        <v>6984</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="D7" t="n">
-        <v>128</v>
+        <v>47</v>
       </c>
       <c r="E7" t="n">
-        <v>20203</v>
+        <v>13575</v>
       </c>
       <c r="F7" t="n">
-        <v>165389</v>
+        <v>79623</v>
       </c>
       <c r="G7" t="n">
-        <v>189194</v>
+        <v>57325</v>
       </c>
       <c r="H7" t="n">
-        <v>1605027</v>
+        <v>337178</v>
       </c>
       <c r="I7" t="n">
-        <v>56207</v>
+        <v>21593</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3240</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118437</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30304</v>
+        <v>7594</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>805</v>
+        <v>152</v>
       </c>
       <c r="D8" t="n">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="E8" t="n">
-        <v>901</v>
+        <v>579</v>
       </c>
       <c r="F8" t="n">
-        <v>4298</v>
+        <v>2708</v>
       </c>
       <c r="G8" t="n">
-        <v>4335</v>
+        <v>2326</v>
       </c>
       <c r="H8" t="n">
-        <v>134607</v>
+        <v>47185</v>
       </c>
       <c r="I8" t="n">
-        <v>628144</v>
+        <v>140360</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
